--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/5493-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/5493-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3402E5B9-A5DE-4914-93D2-9123EC263CD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9FCC607D-7197-4A22-A399-40B37E1BC144}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{8DA847A2-889C-4D18-A5A8-53F97C86D6F9}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{B3272A4C-8D81-41FA-8D02-19A101747684}"/>
   </bookViews>
   <sheets>
     <sheet name="5493-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1490,23 +1490,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55500A0C-82CE-43C5-8399-3DD9FFFBB351}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B32148C-5DB1-443E-86FE-61285C5B5D2F}">
   <dimension ref="A1:R50"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.77734375" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="6" width="10.5" customWidth="1"/>
+    <col min="7" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1534,7 +1534,7 @@
       <c r="Q1" s="31"/>
       <c r="R1" s="23"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
@@ -1564,7 +1564,7 @@
       <c r="Q2" s="33"/>
       <c r="R2" s="34"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
@@ -1610,7 +1610,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="7"/>
@@ -1660,7 +1660,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="38">
         <v>2026</v>
       </c>
@@ -1714,7 +1714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>26</v>
       </c>
@@ -1770,7 +1770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="40">
         <v>2025</v>
       </c>
@@ -1824,7 +1824,7 @@
         <v>2.79</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>26</v>
       </c>
@@ -1880,7 +1880,7 @@
         <v>2.79</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>26</v>
       </c>
@@ -1936,7 +1936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="38">
         <v>2024</v>
       </c>
@@ -1990,7 +1990,7 @@
         <v>3.11</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>26</v>
       </c>
@@ -2046,7 +2046,7 @@
         <v>3.11</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="40">
         <v>2023</v>
       </c>
@@ -2100,7 +2100,7 @@
         <v>5.19</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="s">
         <v>26</v>
       </c>
@@ -2156,7 +2156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
         <v>26</v>
       </c>
@@ -2212,7 +2212,7 @@
         <v>5.19</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="38">
         <v>2022</v>
       </c>
@@ -2266,7 +2266,7 @@
         <v>6.25</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>26</v>
       </c>
@@ -2322,7 +2322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>26</v>
       </c>
@@ -2378,7 +2378,7 @@
         <v>6.25</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>26</v>
       </c>
@@ -2434,7 +2434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="40">
         <v>2021</v>
       </c>
@@ -2488,7 +2488,7 @@
         <v>4.6900000000000004</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
         <v>26</v>
       </c>
@@ -2544,7 +2544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>26</v>
       </c>
@@ -2600,7 +2600,7 @@
         <v>4.6900000000000004</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>26</v>
       </c>
@@ -2656,7 +2656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="38">
         <v>2020</v>
       </c>
@@ -2710,7 +2710,7 @@
         <v>5.81</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>26</v>
       </c>
@@ -2766,7 +2766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>26</v>
       </c>
@@ -2822,7 +2822,7 @@
         <v>5.81</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="40">
         <v>2019</v>
       </c>
@@ -2876,7 +2876,7 @@
         <v>5.83</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="17" t="s">
         <v>26</v>
       </c>
@@ -2932,7 +2932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="17" t="s">
         <v>26</v>
       </c>
@@ -2988,7 +2988,7 @@
         <v>5.83</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="38">
         <v>2018</v>
       </c>
@@ -3042,7 +3042,7 @@
         <v>5.63</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="40">
         <v>2017</v>
       </c>
@@ -3096,7 +3096,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="38">
         <v>2016</v>
       </c>
@@ -3150,7 +3150,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="40">
         <v>2015</v>
       </c>
@@ -3204,7 +3204,7 @@
         <v>5.57</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="38">
         <v>2014</v>
       </c>
@@ -3258,7 +3258,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="40">
         <v>2013</v>
       </c>
@@ -3312,7 +3312,7 @@
         <v>5.54</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="38">
         <v>2012</v>
       </c>
@@ -3366,7 +3366,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="40">
         <v>2011</v>
       </c>
@@ -3420,7 +3420,7 @@
         <v>7.74</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="38">
         <v>2010</v>
       </c>
@@ -3474,7 +3474,7 @@
         <v>4.43</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="40">
         <v>2009</v>
       </c>
@@ -3528,7 +3528,7 @@
         <v>5.34</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="38">
         <v>2008</v>
       </c>
@@ -3582,7 +3582,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="40">
         <v>2007</v>
       </c>
@@ -3636,7 +3636,7 @@
         <v>2.83</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="38">
         <v>2006</v>
       </c>
@@ -3690,7 +3690,7 @@
         <v>6.56</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="40">
         <v>2005</v>
       </c>
@@ -3744,7 +3744,7 @@
         <v>6.71</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="38">
         <v>2004</v>
       </c>
@@ -3798,7 +3798,7 @@
         <v>3.53</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="40">
         <v>2003</v>
       </c>
@@ -3852,7 +3852,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="38">
         <v>2002</v>
       </c>
@@ -3906,7 +3906,7 @@
         <v>8.85</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="40">
         <v>2001</v>
       </c>
@@ -3960,7 +3960,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="38">
         <v>2000</v>
       </c>
@@ -4014,7 +4014,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="40">
         <v>1999</v>
       </c>
@@ -4068,7 +4068,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="49" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="38">
         <v>1998</v>
       </c>
@@ -4122,7 +4122,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="50" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="40" t="s">
         <v>48</v>
       </c>
